--- a/FischerTropsch_Paper/Patagonien_FischerTropsch_5_Naphta_Bio_H2_FT_Brownfield_MH/Datenbank.xlsx
+++ b/FischerTropsch_Paper/Patagonien_FischerTropsch_5_Naphta_Bio_H2_FT_Brownfield_MH/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\FischerTropsch_Paper_Michi\Patagonien_FischerTropsch_5_Naphta_Bio_H2_FT_Brownfield_MH\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\FischerTropsch_Paper\Patagonien_FischerTropsch_5_Naphta_Bio_H2_FT_Brownfield_MH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D93EEB2B-D033-4C51-B731-4F5562E73727}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60346520-2627-4BF1-B257-99B7695B0B58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-4455" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-6945" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -172,7 +172,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="698" uniqueCount="414">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -1410,6 +1410,12 @@
   </si>
   <si>
     <t>kg</t>
+  </si>
+  <si>
+    <t>Landesspezifischer Zinssatz</t>
+  </si>
+  <si>
+    <t>wacc_change</t>
   </si>
 </sst>
 </file>
@@ -1675,9 +1681,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1686,6 +1689,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2023,24 +2029,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G79"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:G80"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="24" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.6328125" style="24" customWidth="1"/>
+    <col min="3" max="3" width="36.1796875" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.81640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.90625" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="11" max="11" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.90625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
@@ -2061,7 +2067,7 @@
       </c>
       <c r="G1" s="24"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" s="43" t="s">
         <v>70</v>
       </c>
@@ -2081,7 +2087,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="44"/>
       <c r="B3" s="51"/>
       <c r="C3" s="1" t="s">
@@ -2097,7 +2103,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="44"/>
       <c r="B4" s="51"/>
       <c r="C4" s="1" t="s">
@@ -2113,7 +2119,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="44"/>
       <c r="B5" s="51"/>
       <c r="C5" s="1" t="s">
@@ -2129,7 +2135,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="44"/>
       <c r="B6" s="51"/>
       <c r="C6" s="1" t="s">
@@ -2145,7 +2151,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="44"/>
       <c r="B7" s="51"/>
       <c r="C7" s="1" t="s">
@@ -2161,7 +2167,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="44"/>
       <c r="B8" s="54" t="s">
         <v>299</v>
@@ -2179,7 +2185,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="44"/>
       <c r="B9" s="51"/>
       <c r="C9" s="1" t="s">
@@ -2195,7 +2201,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="44"/>
       <c r="B10" s="51"/>
       <c r="C10" s="1" t="s">
@@ -2211,7 +2217,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="44"/>
       <c r="B11" s="51"/>
       <c r="C11" s="1" t="s">
@@ -2228,7 +2234,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="44"/>
       <c r="B12" s="51"/>
       <c r="C12" s="1" t="s">
@@ -2244,7 +2250,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="44"/>
       <c r="B13" s="51"/>
       <c r="C13" s="1" t="s">
@@ -2260,7 +2266,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="44"/>
       <c r="B14" s="51"/>
       <c r="C14" s="1" t="s">
@@ -2276,7 +2282,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="44"/>
       <c r="B15" s="51"/>
       <c r="C15" s="1" t="s">
@@ -2292,7 +2298,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="44"/>
       <c r="B16" s="55"/>
       <c r="C16" s="17" t="s">
@@ -2308,7 +2314,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="44"/>
       <c r="B17" s="54" t="s">
         <v>236</v>
@@ -2326,7 +2332,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="44"/>
       <c r="B18" s="51"/>
       <c r="C18" s="1" t="s">
@@ -2342,7 +2348,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="44"/>
       <c r="B19" s="51"/>
       <c r="C19" s="1" t="s">
@@ -2358,7 +2364,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="44"/>
       <c r="B20" s="51"/>
       <c r="C20" s="1" t="s">
@@ -2374,7 +2380,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="44"/>
       <c r="B21" s="51"/>
       <c r="C21" s="1" t="s">
@@ -2390,7 +2396,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="44"/>
       <c r="B22" s="55"/>
       <c r="C22" s="17" t="s">
@@ -2406,7 +2412,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="44"/>
       <c r="B23" s="42" t="s">
         <v>382</v>
@@ -2424,7 +2430,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="44"/>
       <c r="B24" s="42"/>
       <c r="C24" s="1" t="s">
@@ -2440,7 +2446,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="44"/>
       <c r="B25" s="42"/>
       <c r="C25" s="1" t="s">
@@ -2456,7 +2462,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="44"/>
       <c r="B26" s="42"/>
       <c r="C26" s="1" t="s">
@@ -2472,7 +2478,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="44"/>
       <c r="B27" s="42"/>
       <c r="C27" s="1" t="s">
@@ -2488,7 +2494,7 @@
         <v>389</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="44"/>
       <c r="B28" s="42"/>
       <c r="C28" s="1" t="s">
@@ -2504,7 +2510,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="44"/>
       <c r="B29" s="42"/>
       <c r="C29" s="1" t="s">
@@ -2520,7 +2526,7 @@
         <v>395</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="44"/>
       <c r="B30" s="42"/>
       <c r="C30" s="1" t="s">
@@ -2536,7 +2542,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A31" s="44"/>
       <c r="B31" s="42"/>
       <c r="C31" s="1" t="s">
@@ -2552,7 +2558,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="43" t="s">
         <v>71</v>
       </c>
@@ -2572,7 +2578,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="44"/>
       <c r="B33" s="47"/>
       <c r="C33" s="1" t="s">
@@ -2588,7 +2594,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="44"/>
       <c r="B34" s="47"/>
       <c r="C34" s="1" t="s">
@@ -2604,7 +2610,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="44"/>
       <c r="B35" s="47"/>
       <c r="C35" s="1" t="s">
@@ -2620,7 +2626,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="44"/>
       <c r="B36" s="47"/>
       <c r="C36" s="1" t="s">
@@ -2636,7 +2642,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="44"/>
       <c r="B37" s="47"/>
       <c r="C37" s="1" t="s">
@@ -2652,7 +2658,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="44"/>
       <c r="B38" s="47"/>
       <c r="C38" s="1" t="s">
@@ -2668,7 +2674,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A39" s="44"/>
       <c r="B39" s="48"/>
       <c r="C39" s="17" t="s">
@@ -2684,7 +2690,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="44"/>
       <c r="B40" s="49" t="s">
         <v>274</v>
@@ -2702,7 +2708,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="44"/>
       <c r="B41" s="47"/>
       <c r="C41" s="1" t="s">
@@ -2718,7 +2724,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="44"/>
       <c r="B42" s="47"/>
       <c r="C42" s="1" t="s">
@@ -2734,7 +2740,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="44"/>
       <c r="B43" s="47"/>
       <c r="C43" s="1" t="s">
@@ -2750,7 +2756,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="44"/>
       <c r="B44" s="47"/>
       <c r="C44" s="1" t="s">
@@ -2766,7 +2772,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="44"/>
       <c r="B45" s="47"/>
       <c r="C45" s="1" t="s">
@@ -2782,7 +2788,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46" s="44"/>
       <c r="B46" s="47"/>
       <c r="C46" s="1" t="s">
@@ -2798,7 +2804,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47" s="44"/>
       <c r="B47" s="47"/>
       <c r="C47" s="17" t="s">
@@ -2814,7 +2820,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="44"/>
       <c r="B48" s="49" t="s">
         <v>201</v>
@@ -2832,7 +2838,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="44"/>
       <c r="B49" s="51"/>
       <c r="C49" s="1" t="s">
@@ -2849,7 +2855,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="44"/>
       <c r="B50" s="51"/>
       <c r="C50" s="1" t="s">
@@ -2865,7 +2871,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="44"/>
       <c r="B51" s="51"/>
       <c r="C51" s="1" t="s">
@@ -2881,7 +2887,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="44"/>
       <c r="B52" s="51"/>
       <c r="C52" s="1" t="s">
@@ -2897,7 +2903,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="44"/>
       <c r="B53" s="51"/>
       <c r="C53" s="1" t="s">
@@ -2913,7 +2919,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="44"/>
       <c r="B54" s="51"/>
       <c r="C54" s="1" t="s">
@@ -2929,7 +2935,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="44"/>
       <c r="B55" s="51"/>
       <c r="C55" s="1" t="s">
@@ -2945,7 +2951,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="44"/>
       <c r="B56" s="51"/>
       <c r="C56" s="1" t="s">
@@ -2961,7 +2967,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A57" s="45"/>
       <c r="B57" s="52"/>
       <c r="C57" s="27" t="s">
@@ -2977,7 +2983,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="13.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" ht="13.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="43" t="s">
         <v>72</v>
       </c>
@@ -2997,7 +3003,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="44"/>
       <c r="B59" s="39" t="s">
         <v>401</v>
@@ -3015,7 +3021,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="44"/>
       <c r="B60" s="36" t="s">
         <v>376</v>
@@ -3033,7 +3039,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="44"/>
       <c r="B61" s="49" t="s">
         <v>4</v>
@@ -3051,7 +3057,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="44"/>
       <c r="B62" s="47"/>
       <c r="C62" s="1" t="s">
@@ -3067,7 +3073,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="44"/>
       <c r="B63" s="47"/>
       <c r="C63" s="1" t="s">
@@ -3083,7 +3089,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="44"/>
       <c r="B64" s="47"/>
       <c r="C64" s="1" t="s">
@@ -3099,7 +3105,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="44"/>
       <c r="B65" s="47"/>
       <c r="C65" s="1" t="s">
@@ -3115,7 +3121,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="44"/>
       <c r="B66" s="47"/>
       <c r="C66" s="1" t="s">
@@ -3131,7 +3137,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="44"/>
       <c r="B67" s="48"/>
       <c r="C67" s="17" t="s">
@@ -3147,7 +3153,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="44"/>
       <c r="B68" s="49" t="s">
         <v>5</v>
@@ -3165,7 +3171,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="44"/>
       <c r="B69" s="47"/>
       <c r="C69" s="1" t="s">
@@ -3181,7 +3187,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="44"/>
       <c r="B70" s="47"/>
       <c r="C70" s="1" t="s">
@@ -3197,7 +3203,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="44"/>
       <c r="B71" s="47"/>
       <c r="C71" s="1" t="s">
@@ -3213,7 +3219,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="44"/>
       <c r="B72" s="47"/>
       <c r="C72" s="1" t="s">
@@ -3229,7 +3235,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="44"/>
       <c r="B73" s="47"/>
       <c r="C73" s="1" t="s">
@@ -3245,7 +3251,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="45"/>
       <c r="B74" s="50"/>
       <c r="C74" s="27" t="s">
@@ -3261,7 +3267,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="43" t="s">
         <v>76</v>
       </c>
@@ -3281,7 +3287,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="44"/>
       <c r="B76" s="24" t="s">
         <v>259</v>
@@ -3299,7 +3305,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="44"/>
       <c r="B77" s="33" t="s">
         <v>79</v>
@@ -3317,7 +3323,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78" s="44"/>
       <c r="B78" s="33" t="s">
         <v>340</v>
@@ -3335,7 +3341,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A79" s="45"/>
       <c r="B79" s="22" t="s">
         <v>300</v>
@@ -3352,6 +3358,26 @@
       </c>
       <c r="F79" s="27" t="s">
         <v>314</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A80" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B80" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D80" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E80" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="F80" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3379,18 +3405,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
   <dimension ref="A1:F155"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.54296875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="14.54296875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="30.36328125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.81640625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="46.08984375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.54296875" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="11.54296875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A1" s="21" t="s">
         <v>69</v>
       </c>
@@ -3410,7 +3436,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" s="43" t="s">
         <v>70</v>
       </c>
@@ -3428,7 +3454,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" s="44"/>
       <c r="B3" s="51"/>
       <c r="C3" s="1" t="s">
@@ -3442,7 +3468,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" s="44"/>
       <c r="B4" s="51"/>
       <c r="C4" s="1" t="s">
@@ -3456,7 +3482,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" s="44"/>
       <c r="B5" s="51"/>
       <c r="C5" s="1" t="s">
@@ -3470,7 +3496,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="44"/>
       <c r="B6" s="51"/>
       <c r="C6" s="1" t="s">
@@ -3484,7 +3510,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="44"/>
       <c r="B7" s="51"/>
       <c r="C7" s="1" t="s">
@@ -3498,7 +3524,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="44"/>
       <c r="B8" s="51"/>
       <c r="C8" s="1" t="s">
@@ -3512,7 +3538,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="44"/>
       <c r="B9" s="51"/>
       <c r="C9" s="1" t="s">
@@ -3526,7 +3552,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="44"/>
       <c r="B10" s="51"/>
       <c r="C10" s="1" t="s">
@@ -3540,12 +3566,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="44"/>
       <c r="B11" s="51"/>
       <c r="E11" s="3"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" s="44"/>
       <c r="B12" s="54" t="s">
         <v>333</v>
@@ -3561,7 +3587,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="44"/>
       <c r="B13" s="51"/>
       <c r="C13" s="1" t="s">
@@ -3575,7 +3601,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="44"/>
       <c r="B14" s="51"/>
       <c r="C14" s="1" t="s">
@@ -3589,7 +3615,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" s="44"/>
       <c r="B15" s="51"/>
       <c r="C15" s="1" t="s">
@@ -3603,7 +3629,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" s="44"/>
       <c r="B16" s="51"/>
       <c r="C16" s="1" t="s">
@@ -3617,7 +3643,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="44"/>
       <c r="B17" s="51"/>
       <c r="C17" s="1" t="s">
@@ -3631,7 +3657,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" s="44"/>
       <c r="B18" s="51"/>
       <c r="C18" s="1" t="s">
@@ -3645,7 +3671,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="44"/>
       <c r="B19" s="51"/>
       <c r="C19" s="1" t="s">
@@ -3659,7 +3685,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="44"/>
       <c r="B20" s="51"/>
       <c r="C20" s="1" t="s">
@@ -3673,7 +3699,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="44"/>
       <c r="B21" s="51"/>
       <c r="C21" s="1" t="s">
@@ -3687,7 +3713,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22" s="44"/>
       <c r="B22" s="51"/>
       <c r="C22" s="1" t="s">
@@ -3701,7 +3727,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" s="44"/>
       <c r="B23" s="55"/>
       <c r="C23" s="17"/>
@@ -3709,7 +3735,7 @@
       <c r="E23" s="18"/>
       <c r="F23" s="17"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" s="44"/>
       <c r="B24" s="54" t="s">
         <v>236</v>
@@ -3725,7 +3751,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" s="44"/>
       <c r="B25" s="51"/>
       <c r="C25" s="1" t="s">
@@ -3739,7 +3765,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" s="44"/>
       <c r="B26" s="51"/>
       <c r="C26" s="1" t="s">
@@ -3753,7 +3779,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" s="44"/>
       <c r="B27" s="51"/>
       <c r="C27" s="1" t="s">
@@ -3767,7 +3793,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28" s="44"/>
       <c r="B28" s="51"/>
       <c r="C28" s="1" t="s">
@@ -3781,7 +3807,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29" s="44"/>
       <c r="B29" s="51"/>
       <c r="C29" s="1" t="s">
@@ -3795,7 +3821,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30" s="44"/>
       <c r="B30" s="51"/>
       <c r="C30" s="1" t="s">
@@ -3809,7 +3835,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31" s="44"/>
       <c r="B31" s="51"/>
       <c r="C31" s="1" t="s">
@@ -3823,7 +3849,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32" s="44"/>
       <c r="B32" s="51"/>
       <c r="C32" s="1" t="s">
@@ -3837,7 +3863,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33" s="44"/>
       <c r="B33" s="55"/>
       <c r="C33" s="17"/>
@@ -3845,7 +3871,7 @@
       <c r="E33" s="18"/>
       <c r="F33" s="17"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34" s="44"/>
       <c r="B34" s="42" t="s">
         <v>361</v>
@@ -3861,7 +3887,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35" s="44"/>
       <c r="B35" s="42"/>
       <c r="C35" s="1" t="s">
@@ -3875,7 +3901,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36" s="44"/>
       <c r="B36" s="42"/>
       <c r="C36" s="1" t="s">
@@ -3889,7 +3915,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37" s="44"/>
       <c r="B37" s="42"/>
       <c r="C37" s="1" t="s">
@@ -3903,7 +3929,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38" s="44"/>
       <c r="B38" s="42"/>
       <c r="C38" s="1" t="s">
@@ -3917,7 +3943,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39" s="44"/>
       <c r="B39" s="42"/>
       <c r="C39" s="1" t="s">
@@ -3931,7 +3957,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40" s="44"/>
       <c r="B40" s="42"/>
       <c r="C40" s="1" t="s">
@@ -3945,7 +3971,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41" s="44"/>
       <c r="B41" s="42"/>
       <c r="C41" s="1" t="s">
@@ -3959,7 +3985,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42" s="44"/>
       <c r="B42" s="42"/>
       <c r="C42" s="1" t="s">
@@ -3973,7 +3999,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43" s="44"/>
       <c r="B43" s="42"/>
       <c r="C43" s="1" t="s">
@@ -3987,7 +4013,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44" s="44"/>
       <c r="B44" s="42"/>
       <c r="C44" s="1" t="s">
@@ -4001,7 +4027,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45" s="44"/>
       <c r="B45" s="42"/>
       <c r="C45" s="1" t="s">
@@ -4015,12 +4041,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A46" s="44"/>
       <c r="B46" s="42"/>
       <c r="E46" s="3"/>
     </row>
-    <row r="47" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="43" t="s">
         <v>71</v>
       </c>
@@ -4038,7 +4064,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48" s="44"/>
       <c r="B48" s="47"/>
       <c r="C48" s="1" t="s">
@@ -4052,7 +4078,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" s="44"/>
       <c r="B49" s="47"/>
       <c r="C49" s="1" t="s">
@@ -4066,7 +4092,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" s="44"/>
       <c r="B50" s="47"/>
       <c r="C50" s="1" t="s">
@@ -4080,7 +4106,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" s="44"/>
       <c r="B51" s="47"/>
       <c r="C51" s="1" t="s">
@@ -4094,7 +4120,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" s="44"/>
       <c r="B52" s="47"/>
       <c r="C52" s="1" t="s">
@@ -4108,7 +4134,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53" s="44"/>
       <c r="B53" s="47"/>
       <c r="C53" s="1" t="s">
@@ -4122,7 +4148,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54" s="44"/>
       <c r="B54" s="47"/>
       <c r="C54" s="1" t="s">
@@ -4136,7 +4162,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55" s="44"/>
       <c r="B55" s="47"/>
       <c r="C55" s="1" t="s">
@@ -4150,7 +4176,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56" s="44"/>
       <c r="B56" s="48"/>
       <c r="C56" s="17"/>
@@ -4158,7 +4184,7 @@
       <c r="E56" s="18"/>
       <c r="F56" s="17"/>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57" s="44"/>
       <c r="B57" s="47" t="s">
         <v>274</v>
@@ -4174,7 +4200,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58" s="44"/>
       <c r="B58" s="47"/>
       <c r="C58" s="1" t="s">
@@ -4188,7 +4214,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59" s="44"/>
       <c r="B59" s="47"/>
       <c r="C59" s="1" t="s">
@@ -4202,7 +4228,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60" s="44"/>
       <c r="B60" s="47"/>
       <c r="C60" s="1" t="s">
@@ -4216,7 +4242,7 @@
         <v>360</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61" s="44"/>
       <c r="B61" s="47"/>
       <c r="C61" s="1" t="s">
@@ -4230,7 +4256,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62" s="44"/>
       <c r="B62" s="47"/>
       <c r="C62" s="1" t="s">
@@ -4244,7 +4270,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63" s="44"/>
       <c r="B63" s="47"/>
       <c r="C63" s="1" t="s">
@@ -4258,7 +4284,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64" s="44"/>
       <c r="B64" s="47"/>
       <c r="C64" s="1" t="s">
@@ -4272,7 +4298,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65" s="44"/>
       <c r="B65" s="47"/>
       <c r="C65" s="1" t="s">
@@ -4286,12 +4312,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66" s="44"/>
       <c r="B66" s="48"/>
       <c r="E66" s="3"/>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67" s="44"/>
       <c r="B67" s="49" t="s">
         <v>6</v>
@@ -4307,7 +4333,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68" s="44"/>
       <c r="B68" s="47"/>
       <c r="C68" s="1" t="s">
@@ -4321,7 +4347,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69" s="44"/>
       <c r="B69" s="51"/>
       <c r="C69" s="1" t="s">
@@ -4335,7 +4361,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70" s="44"/>
       <c r="B70" s="51"/>
       <c r="C70" s="1" t="s">
@@ -4349,7 +4375,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71" s="44"/>
       <c r="B71" s="51"/>
       <c r="C71" s="1" t="s">
@@ -4363,7 +4389,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72" s="44"/>
       <c r="B72" s="51"/>
       <c r="C72" s="1" t="s">
@@ -4377,7 +4403,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73" s="44"/>
       <c r="B73" s="51"/>
       <c r="C73" s="1" t="s">
@@ -4391,7 +4417,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74" s="44"/>
       <c r="B74" s="51"/>
       <c r="C74" s="1" t="s">
@@ -4405,7 +4431,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75" s="44"/>
       <c r="B75" s="51"/>
       <c r="C75" s="1" t="s">
@@ -4419,7 +4445,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76" s="44"/>
       <c r="B76" s="51"/>
       <c r="C76" s="1" t="s">
@@ -4433,7 +4459,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77" s="44"/>
       <c r="B77" s="51"/>
       <c r="C77" s="1" t="s">
@@ -4447,7 +4473,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A78" s="45"/>
       <c r="B78" s="52"/>
       <c r="C78" s="27"/>
@@ -4455,7 +4481,7 @@
       <c r="E78" s="28"/>
       <c r="F78" s="27"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79" s="43" t="s">
         <v>72</v>
       </c>
@@ -4473,7 +4499,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80" s="44"/>
       <c r="B80" s="51"/>
       <c r="C80" s="1" t="s">
@@ -4487,7 +4513,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81" s="44"/>
       <c r="B81" s="55"/>
       <c r="C81" s="17"/>
@@ -4495,9 +4521,9 @@
       <c r="E81" s="38"/>
       <c r="F81" s="17"/>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82" s="44"/>
-      <c r="B82" s="58" t="s">
+      <c r="B82" s="57" t="s">
         <v>404</v>
       </c>
       <c r="C82" s="15" t="s">
@@ -4511,9 +4537,9 @@
         <v>132</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83" s="44"/>
-      <c r="B83" s="57"/>
+      <c r="B83" s="56"/>
       <c r="C83" s="1" t="s">
         <v>407</v>
       </c>
@@ -4525,17 +4551,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84" s="44"/>
-      <c r="B84" s="59"/>
+      <c r="B84" s="58"/>
       <c r="C84" s="17"/>
       <c r="D84" s="17"/>
       <c r="E84" s="38"/>
       <c r="F84" s="17"/>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85" s="44"/>
-      <c r="B85" s="57" t="s">
+      <c r="B85" s="56" t="s">
         <v>376</v>
       </c>
       <c r="C85" s="1" t="s">
@@ -4549,9 +4575,9 @@
         <v>379</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86" s="44"/>
-      <c r="B86" s="57"/>
+      <c r="B86" s="56"/>
       <c r="C86" s="1" t="s">
         <v>380</v>
       </c>
@@ -4563,12 +4589,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87" s="44"/>
-      <c r="B87" s="57"/>
+      <c r="B87" s="56"/>
       <c r="E87" s="2"/>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88" s="44"/>
       <c r="B88" s="49" t="s">
         <v>4</v>
@@ -4584,7 +4610,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89" s="44"/>
       <c r="B89" s="47"/>
       <c r="C89" s="1" t="s">
@@ -4598,7 +4624,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90" s="44"/>
       <c r="B90" s="47"/>
       <c r="C90" s="1" t="s">
@@ -4612,7 +4638,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91" s="44"/>
       <c r="B91" s="47"/>
       <c r="C91" s="1" t="s">
@@ -4626,7 +4652,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92" s="44"/>
       <c r="B92" s="47"/>
       <c r="C92" s="1" t="s">
@@ -4640,7 +4666,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93" s="44"/>
       <c r="B93" s="47"/>
       <c r="C93" s="1" t="s">
@@ -4654,7 +4680,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94" s="44"/>
       <c r="B94" s="47"/>
       <c r="C94" s="1" t="s">
@@ -4668,7 +4694,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95" s="44"/>
       <c r="B95" s="47"/>
       <c r="C95" s="1" t="s">
@@ -4682,7 +4708,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96" s="44"/>
       <c r="B96" s="47"/>
       <c r="C96" s="1" t="s">
@@ -4696,11 +4722,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97" s="44"/>
       <c r="B97" s="48"/>
     </row>
-    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A98" s="44"/>
       <c r="B98" s="49" t="s">
         <v>5</v>
@@ -4716,7 +4742,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A99" s="44"/>
       <c r="B99" s="47"/>
       <c r="C99" s="1" t="s">
@@ -4730,7 +4756,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A100" s="44"/>
       <c r="B100" s="47"/>
       <c r="C100" s="1" t="s">
@@ -4744,7 +4770,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A101" s="44"/>
       <c r="B101" s="47"/>
       <c r="C101" s="1" t="s">
@@ -4758,7 +4784,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A102" s="44"/>
       <c r="B102" s="47"/>
       <c r="C102" s="1" t="s">
@@ -4772,7 +4798,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A103" s="44"/>
       <c r="B103" s="47"/>
       <c r="C103" s="1" t="s">
@@ -4786,7 +4812,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A104" s="44"/>
       <c r="B104" s="47"/>
       <c r="C104" s="1" t="s">
@@ -4800,7 +4826,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A105" s="44"/>
       <c r="B105" s="47"/>
       <c r="C105" s="1" t="s">
@@ -4814,7 +4840,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A106" s="44"/>
       <c r="B106" s="47"/>
       <c r="C106" s="1" t="s">
@@ -4828,11 +4854,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="107" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A107" s="45"/>
       <c r="B107" s="50"/>
     </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A108" s="43" t="s">
         <v>76</v>
       </c>
@@ -4850,7 +4876,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A109" s="44"/>
       <c r="B109" s="51"/>
       <c r="C109" s="1" t="s">
@@ -4864,7 +4890,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A110" s="44"/>
       <c r="B110" s="55"/>
       <c r="C110" s="17"/>
@@ -4872,7 +4898,7 @@
       <c r="E110" s="18"/>
       <c r="F110" s="17"/>
     </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A111" s="44"/>
       <c r="B111" s="54" t="s">
         <v>263</v>
@@ -4888,7 +4914,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A112" s="44"/>
       <c r="B112" s="51"/>
       <c r="C112" s="1" t="s">
@@ -4902,12 +4928,12 @@
         <v>149</v>
       </c>
     </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A113" s="44"/>
       <c r="B113" s="55"/>
       <c r="E113" s="3"/>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A114" s="44"/>
       <c r="B114" s="54" t="s">
         <v>79</v>
@@ -4923,7 +4949,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A115" s="44"/>
       <c r="B115" s="51"/>
       <c r="C115" s="1" t="s">
@@ -4937,7 +4963,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A116" s="44"/>
       <c r="B116" s="55"/>
       <c r="C116" s="17"/>
@@ -4945,7 +4971,7 @@
       <c r="E116" s="18"/>
       <c r="F116" s="17"/>
     </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A117" s="44"/>
       <c r="B117" s="54" t="s">
         <v>340</v>
@@ -4961,7 +4987,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A118" s="44"/>
       <c r="B118" s="51"/>
       <c r="C118" s="1" t="s">
@@ -4975,7 +5001,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A119" s="44"/>
       <c r="B119" s="55"/>
       <c r="C119" s="17"/>
@@ -4983,7 +5009,7 @@
       <c r="E119" s="18"/>
       <c r="F119" s="17"/>
     </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A120" s="44"/>
       <c r="B120" s="51" t="s">
         <v>300</v>
@@ -4999,7 +5025,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A121" s="44"/>
       <c r="B121" s="51"/>
       <c r="C121" s="1" t="s">
@@ -5013,7 +5039,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="122" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A122" s="45"/>
       <c r="B122" s="52"/>
       <c r="C122" s="27"/>
@@ -5021,7 +5047,7 @@
       <c r="E122" s="28"/>
       <c r="F122" s="27"/>
     </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A123" s="43" t="s">
         <v>163</v>
       </c>
@@ -5039,7 +5065,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A124" s="44"/>
       <c r="B124" s="51"/>
       <c r="C124" s="1" t="s">
@@ -5052,7 +5078,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A125" s="44"/>
       <c r="B125" s="55"/>
       <c r="C125" s="17"/>
@@ -5060,7 +5086,7 @@
       <c r="E125" s="17"/>
       <c r="F125" s="17"/>
     </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A126" s="44"/>
       <c r="B126" s="54" t="s">
         <v>183</v>
@@ -5075,7 +5101,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A127" s="44"/>
       <c r="B127" s="51"/>
       <c r="C127" s="1" t="s">
@@ -5088,7 +5114,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A128" s="44"/>
       <c r="B128" s="51"/>
       <c r="C128" s="1" t="s">
@@ -5101,7 +5127,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A129" s="44"/>
       <c r="B129" s="51"/>
       <c r="C129" s="1" t="s">
@@ -5114,7 +5140,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A130" s="44"/>
       <c r="B130" s="51"/>
       <c r="C130" s="1" t="s">
@@ -5127,7 +5153,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A131" s="44"/>
       <c r="B131" s="51"/>
       <c r="C131" s="1" t="s">
@@ -5140,11 +5166,11 @@
         <v>149</v>
       </c>
     </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A132" s="44"/>
       <c r="B132" s="55"/>
     </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A133" s="44"/>
       <c r="B133" s="54" t="s">
         <v>206</v>
@@ -5160,7 +5186,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A134" s="44"/>
       <c r="B134" s="51"/>
       <c r="C134" s="1" t="s">
@@ -5173,7 +5199,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A135" s="44"/>
       <c r="B135" s="51"/>
       <c r="C135" s="1" t="s">
@@ -5186,7 +5212,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A136" s="44"/>
       <c r="B136" s="51"/>
       <c r="C136" s="1" t="s">
@@ -5199,7 +5225,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A137" s="44"/>
       <c r="B137" s="51"/>
       <c r="C137" s="1" t="s">
@@ -5212,7 +5238,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A138" s="44"/>
       <c r="B138" s="51"/>
       <c r="C138" s="1" t="s">
@@ -5225,7 +5251,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A139" s="44"/>
       <c r="B139" s="51"/>
       <c r="C139" s="1" t="s">
@@ -5238,7 +5264,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A140" s="44"/>
       <c r="B140" s="51"/>
       <c r="C140" s="1" t="s">
@@ -5251,7 +5277,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A141" s="44"/>
       <c r="B141" s="51"/>
       <c r="C141" s="1" t="s">
@@ -5264,7 +5290,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A142" s="44"/>
       <c r="B142" s="51"/>
       <c r="C142" s="1" t="s">
@@ -5277,7 +5303,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A143" s="44"/>
       <c r="B143" s="51"/>
       <c r="C143" s="1" t="s">
@@ -5290,7 +5316,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A144" s="44"/>
       <c r="B144" s="51"/>
       <c r="C144" s="1" t="s">
@@ -5303,7 +5329,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A145" s="44"/>
       <c r="B145" s="51"/>
       <c r="C145" s="1" t="s">
@@ -5316,7 +5342,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A146" s="44"/>
       <c r="B146" s="51"/>
       <c r="C146" s="1" t="s">
@@ -5329,11 +5355,11 @@
         <v>213</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A147" s="44"/>
       <c r="B147" s="55"/>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A148" s="44"/>
       <c r="B148" s="54" t="s">
         <v>222</v>
@@ -5349,7 +5375,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A149" s="44"/>
       <c r="B149" s="51"/>
       <c r="C149" s="1" t="s">
@@ -5362,7 +5388,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A150" s="44"/>
       <c r="B150" s="51"/>
       <c r="C150" s="1" t="s">
@@ -5375,7 +5401,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A151" s="44"/>
       <c r="B151" s="51"/>
       <c r="C151" s="1" t="s">
@@ -5388,7 +5414,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A152" s="44"/>
       <c r="B152" s="51"/>
       <c r="C152" s="1" t="s">
@@ -5401,7 +5427,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A153" s="44"/>
       <c r="B153" s="55"/>
       <c r="C153" s="17"/>
@@ -5409,9 +5435,9 @@
       <c r="E153" s="17"/>
       <c r="F153" s="17"/>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A154" s="44"/>
-      <c r="B154" s="56" t="s">
+      <c r="B154" s="59" t="s">
         <v>355</v>
       </c>
       <c r="C154" s="1" t="s">
@@ -5424,9 +5450,9 @@
         <v>314</v>
       </c>
     </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A155" s="44"/>
-      <c r="B155" s="56"/>
+      <c r="B155" s="59"/>
       <c r="C155" s="1" t="s">
         <v>357</v>
       </c>
@@ -5439,15 +5465,12 @@
     </row>
   </sheetData>
   <mergeCells count="27">
-    <mergeCell ref="A2:A46"/>
-    <mergeCell ref="B2:B11"/>
-    <mergeCell ref="B12:B23"/>
-    <mergeCell ref="A47:A78"/>
-    <mergeCell ref="B67:B78"/>
-    <mergeCell ref="B24:B33"/>
-    <mergeCell ref="B47:B56"/>
-    <mergeCell ref="B57:B66"/>
-    <mergeCell ref="B34:B46"/>
+    <mergeCell ref="B148:B153"/>
+    <mergeCell ref="B154:B155"/>
+    <mergeCell ref="A123:A155"/>
+    <mergeCell ref="B123:B125"/>
+    <mergeCell ref="B133:B147"/>
+    <mergeCell ref="B126:B132"/>
     <mergeCell ref="B120:B122"/>
     <mergeCell ref="B79:B81"/>
     <mergeCell ref="A79:A107"/>
@@ -5460,12 +5483,15 @@
     <mergeCell ref="B117:B119"/>
     <mergeCell ref="B85:B87"/>
     <mergeCell ref="B82:B84"/>
-    <mergeCell ref="B148:B153"/>
-    <mergeCell ref="B154:B155"/>
-    <mergeCell ref="A123:A155"/>
-    <mergeCell ref="B123:B125"/>
-    <mergeCell ref="B133:B147"/>
-    <mergeCell ref="B126:B132"/>
+    <mergeCell ref="A2:A46"/>
+    <mergeCell ref="B2:B11"/>
+    <mergeCell ref="B12:B23"/>
+    <mergeCell ref="A47:A78"/>
+    <mergeCell ref="B67:B78"/>
+    <mergeCell ref="B24:B33"/>
+    <mergeCell ref="B47:B56"/>
+    <mergeCell ref="B57:B66"/>
+    <mergeCell ref="B34:B46"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
